--- a/release_forms/003_subcontractor_lien_release_form--release_forms.xlsx
+++ b/release_forms/003_subcontractor_lien_release_form--release_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>subcontractor_lien_release_form_1</t>
+          <t>lien_release_form</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lien_release</t>
+          <t>Lien Release Form</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>subcontractor_lien_release_form_2</t>
+          <t>contractor_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>contractor_name</t>
+          <t>Contractor Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>contractor_address</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contractors_address</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contractor_city</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contractor_state</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>State</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>contractor_zip</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>Zip</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>date_of_completion</t>
+          <t>Date of Completion</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>job_location</t>
+          <t>Job Location</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>job_site_address</t>
+          <t>Job Site Address</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>Job Site City</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>Job Site State</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>Job Site Zip</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>general_contractor_lien_amount</t>
+          <t>lien_amount</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lien_amount</t>
+          <t>Lien Amount</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>contractor_name</t>
+          <t>General Contractor Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>General Contractor Address</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>subcontractor_lien_release</t>
+          <t>release</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>release</t>
+          <t>Release</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>subcontractor_signature</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>job_number</t>
+          <t>Job Number</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>job_description</t>
+          <t>Job Description</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>general_contractor_lien_type</t>
+          <t>lien_type</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>lien_type</t>
+          <t>Lien Type</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,39 +1049,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>job_site_name</t>
+          <t>job_site</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>job_site</t>
+          <t>Job Site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>general_contractor_name_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>contractor_name</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1101,7 +1078,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +1103,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>contractor_state_choices</t>
+          <t>state_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1120,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>contractor_state_choices</t>
+          <t>state_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
